--- a/Experts/Anhnt/Document/MQL5 Note/2026 0407 MVC Refactor.xlsx
+++ b/Experts/Anhnt/Document/MQL5 Note/2026 0407 MVC Refactor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nguye\AppData\Roaming\MetaQuotes\Terminal\D0E8209F77C8CF37AD8BF550E51FF075\MQL5\Experts\Anhnt\Document\MQL5 Note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898017B0-7FED-414F-9C6A-64D397C4AC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FB35D7-2201-4EE6-A6DC-253F8E7DA643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5B521979-E0DC-4D73-A935-0CEFCD7B0287}"/>
   </bookViews>
@@ -441,7 +441,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,6 +463,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -503,16 +509,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -530,6 +530,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2238,1010 +2250,1010 @@
     <col min="1" max="1" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.33203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.33203125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="6" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="7" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="9" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="11" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="7"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="7"/>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="7"/>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="7" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="7"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="7" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="7"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="4"/>
+      <c r="D19" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="7"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="7"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="7"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="7"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="7"/>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="7"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F26" s="7"/>
+      <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="7" t="s">
+      <c r="A28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F28" s="7"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="7" t="s">
+      <c r="A29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F29" s="7"/>
+      <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="10" t="s">
+      <c r="A30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="9"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="5" t="s">
+      <c r="A31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="7"/>
+      <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="5" t="s">
+      <c r="A32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="7" t="s">
+      <c r="D32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="7"/>
+      <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" s="7" t="s">
+      <c r="D33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="7"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="5" t="s">
+      <c r="A34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" s="7" t="s">
+      <c r="D34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F34" s="7"/>
+      <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="5" t="s">
+      <c r="A35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="7" t="s">
+      <c r="D35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F35" s="7"/>
+      <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="7" t="s">
+      <c r="D36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="7"/>
+      <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="5" t="s">
+      <c r="A37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E37" s="7" t="s">
+      <c r="D37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="7"/>
+      <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" s="7" t="s">
+      <c r="D38" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="7"/>
+      <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="A39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="7" t="s">
+      <c r="D39" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="7"/>
+      <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="7" t="s">
+      <c r="D40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F40" s="7"/>
+      <c r="F40" s="5"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" s="7" t="s">
+      <c r="D41" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F41" s="7"/>
+      <c r="F41" s="5"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="A42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="7" t="s">
+      <c r="D42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F42" s="7"/>
+      <c r="F42" s="5"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="A43" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E43" s="7" t="s">
+      <c r="D43" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F43" s="7"/>
+      <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="A44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="7" t="s">
+      <c r="D44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F44" s="7"/>
+      <c r="F44" s="5"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="A45" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E45" s="7" t="s">
+      <c r="D45" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F45" s="7"/>
+      <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" s="5" t="s">
+      <c r="A46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E46" s="7" t="s">
+      <c r="D46" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="7"/>
+      <c r="F46" s="5"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" s="5" t="s">
+      <c r="A47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47" s="7" t="s">
+      <c r="D47" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F47" s="7"/>
+      <c r="F47" s="5"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" s="5" t="s">
+      <c r="A48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E48" s="7" t="s">
+      <c r="D48" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F48" s="7"/>
+      <c r="F48" s="5"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="A49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="7" t="s">
+      <c r="D49" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F49" s="7"/>
+      <c r="F49" s="5"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="A50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="7" t="s">
+      <c r="D50" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F50" s="7"/>
+      <c r="F50" s="5"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="A51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" s="7" t="s">
+      <c r="D51" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F51" s="7"/>
+      <c r="F51" s="5"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B52" s="5" t="s">
+      <c r="A52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" s="7" t="s">
+      <c r="D52" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F52" s="7"/>
+      <c r="F52" s="5"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="5" t="s">
+      <c r="A53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E53" s="7" t="s">
+      <c r="D53" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F53" s="7"/>
+      <c r="F53" s="5"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B54" s="5" t="s">
+      <c r="A54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E54" s="7" t="s">
+      <c r="D54" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F54" s="7"/>
+      <c r="F54" s="5"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B55" s="5" t="s">
+      <c r="A55" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" s="7" t="s">
+      <c r="D55" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F55" s="7"/>
+      <c r="F55" s="5"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="A56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E56" s="7" t="s">
+      <c r="D56" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F56" s="7"/>
+      <c r="F56" s="5"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="A57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E57" s="7" t="s">
+      <c r="D57" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F57" s="7"/>
+      <c r="F57" s="5"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="A58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="7" t="s">
+      <c r="D58" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F58" s="7"/>
+      <c r="F58" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Experts/Anhnt/Document/MQL5 Note/2026 0407 MVC Refactor.xlsx
+++ b/Experts/Anhnt/Document/MQL5 Note/2026 0407 MVC Refactor.xlsx
@@ -8,16 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nguye\AppData\Roaming\MetaQuotes\Terminal\D0E8209F77C8CF37AD8BF550E51FF075\MQL5\Experts\Anhnt\Document\MQL5 Note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FB35D7-2201-4EE6-A6DC-253F8E7DA643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B2EDE1-1A0C-4498-9634-79378B810191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5B521979-E0DC-4D73-A935-0CEFCD7B0287}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{5B521979-E0DC-4D73-A935-0CEFCD7B0287}"/>
   </bookViews>
   <sheets>
     <sheet name="Chưa tách" sheetId="1" r:id="rId1"/>
     <sheet name="Tách" sheetId="2" r:id="rId2"/>
     <sheet name="So sánh" sheetId="3" r:id="rId3"/>
+    <sheet name="LibDeb" sheetId="4" r:id="rId4"/>
+    <sheet name="Class" sheetId="5" r:id="rId5"/>
+    <sheet name="Compile" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Class!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Compile!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LibDeb!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tách!$B$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="151">
   <si>
     <t>File Name</t>
   </si>
@@ -425,6 +431,75 @@
   </si>
   <si>
     <t>Note sau tách</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>1. 17653 Applying the MVC concept</t>
+  </si>
+  <si>
+    <t>1. 17653 Applying the MVC concept Original En.mq5</t>
+  </si>
+  <si>
+    <t>2. 17960 Base graphical element\Original English</t>
+  </si>
+  <si>
+    <t>3. 18221 Lib</t>
+  </si>
+  <si>
+    <t>4. 18658 Containers\Original English</t>
+  </si>
+  <si>
+    <t>18658 iTestContainer_EN.mq5</t>
+  </si>
+  <si>
+    <t>4. 18658 Containers\Original English\Controls</t>
+  </si>
+  <si>
+    <t>5. 18941 Resizable elements</t>
+  </si>
+  <si>
+    <t>18941 iTestResize_EN.mq5</t>
+  </si>
+  <si>
+    <t>6. 19288 Integrating the Model Component into the View Component</t>
+  </si>
+  <si>
+    <t>7. 19979 Customizable and sortable table columns</t>
+  </si>
+  <si>
+    <t>8. 20596 Lib</t>
+  </si>
+  <si>
+    <t>8. 20596 Lib\Controls</t>
+  </si>
+  <si>
+    <t>8. 20596 Refactor\Base</t>
+  </si>
+  <si>
+    <t>8. 20596 Refactor\Collections</t>
+  </si>
+  <si>
+    <t>8. 20596 Refactor\Controls</t>
+  </si>
+  <si>
+    <t>8. 20596 Refactor\Defines</t>
+  </si>
+  <si>
+    <t>8. 20596 Refactor\Services</t>
+  </si>
+  <si>
+    <t>8. 20596 Refactor\Tables</t>
+  </si>
+  <si>
+    <t>8. 20596 Refactor\Temp</t>
+  </si>
+  <si>
+    <t>Compile</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -532,23 +607,34 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2256,16 +2342,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="11" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2285,7 +2371,7 @@
       <c r="E2" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F2" s="11"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -2337,10 +2423,10 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>108</v>
       </c>
       <c r="F6" s="5"/>
@@ -3263,4 +3349,6473 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96CE20C3-9793-4122-9AC2-6F030E0B9A3F}">
+  <dimension ref="A1:E281"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="45.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="47.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>36</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>38</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>39</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>43</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>44</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>47</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>55</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>58</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>59</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>60</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>61</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>63</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>64</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>65</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>66</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>68</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>69</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>70</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>72</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>74</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>76</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>77</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>78</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>79</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>80</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>81</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>82</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>83</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>84</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>85</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>86</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>87</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>88</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>89</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>90</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>91</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>92</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>93</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>94</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>95</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>96</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>97</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>98</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>99</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>100</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>101</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>102</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>103</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>104</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>105</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>106</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>107</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>108</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>109</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>110</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>111</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>112</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>113</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>114</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>115</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>116</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>117</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>118</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>119</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>120</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>121</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>122</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>123</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>124</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>125</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>126</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>127</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>128</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>129</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>130</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>131</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>132</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>133</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>134</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>135</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>136</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <v>137</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="2">
+        <v>138</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="2">
+        <v>139</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="2">
+        <v>140</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="2">
+        <v>141</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <v>142</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="2">
+        <v>143</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="2">
+        <v>144</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="2">
+        <v>145</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="2">
+        <v>146</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="2">
+        <v>147</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="2">
+        <v>148</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="2">
+        <v>149</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
+        <v>150</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="2">
+        <v>151</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>152</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <v>153</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <v>154</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="2">
+        <v>155</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <v>156</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="2">
+        <v>157</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="2">
+        <v>158</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>159</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="2">
+        <v>160</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <v>161</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="2">
+        <v>162</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
+        <v>163</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="2">
+        <v>164</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
+        <v>165</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="2">
+        <v>166</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>167</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="2">
+        <v>168</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <v>169</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="2">
+        <v>170</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="2">
+        <v>171</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="2">
+        <v>172</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="2">
+        <v>173</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <v>174</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
+        <v>175</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="2">
+        <v>176</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
+        <v>177</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>178</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <v>179</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
+        <v>180</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="2">
+        <v>181</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="2">
+        <v>182</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="2">
+        <v>183</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
+        <v>184</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="2">
+        <v>185</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="2">
+        <v>186</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="2">
+        <v>187</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="2">
+        <v>188</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="2">
+        <v>189</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="2">
+        <v>190</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="2">
+        <v>191</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192" s="2">
+        <v>192</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193" s="2">
+        <v>193</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194" s="2">
+        <v>194</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A195" s="2">
+        <v>195</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A196" s="2">
+        <v>196</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A197" s="2">
+        <v>197</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A198" s="2">
+        <v>198</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A199" s="2">
+        <v>199</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A200" s="2">
+        <v>200</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A201" s="2">
+        <v>201</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202" s="2">
+        <v>202</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A203" s="2">
+        <v>203</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A204" s="2">
+        <v>204</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205" s="2">
+        <v>205</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="2">
+        <v>206</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="2">
+        <v>207</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="2">
+        <v>208</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="2">
+        <v>209</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210" s="2">
+        <v>210</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" s="2">
+        <v>211</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" s="2">
+        <v>212</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" s="2">
+        <v>213</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" s="2">
+        <v>214</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215" s="2">
+        <v>215</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216" s="2">
+        <v>216</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217" s="2">
+        <v>217</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A218" s="2">
+        <v>218</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A219" s="2">
+        <v>219</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A220" s="2">
+        <v>220</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A221" s="2">
+        <v>221</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A222" s="2">
+        <v>222</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A223" s="2">
+        <v>223</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A224" s="2">
+        <v>224</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A225" s="2">
+        <v>225</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A226" s="2">
+        <v>226</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A227" s="2">
+        <v>227</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A228" s="2">
+        <v>228</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A229" s="2">
+        <v>229</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A230" s="2">
+        <v>230</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A231" s="2">
+        <v>231</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A232" s="2">
+        <v>232</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A233" s="2">
+        <v>233</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A234" s="2">
+        <v>234</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A235" s="2">
+        <v>235</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A236" s="2">
+        <v>236</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A237" s="2">
+        <v>237</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A238" s="2">
+        <v>238</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A239" s="2">
+        <v>239</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A240" s="2">
+        <v>240</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A241" s="2">
+        <v>241</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A242" s="2">
+        <v>242</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A243" s="2">
+        <v>243</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A244" s="2">
+        <v>244</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A245" s="2">
+        <v>245</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A246" s="2">
+        <v>246</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A247" s="2">
+        <v>247</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A248" s="2">
+        <v>248</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A249" s="2">
+        <v>249</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A250" s="2">
+        <v>250</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A251" s="2">
+        <v>251</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A252" s="2">
+        <v>252</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A253" s="2">
+        <v>253</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A254" s="2">
+        <v>254</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A255" s="2">
+        <v>255</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A256" s="2">
+        <v>256</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A257" s="2">
+        <v>257</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A258" s="2">
+        <v>258</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A259" s="2">
+        <v>259</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A260" s="2">
+        <v>260</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A261" s="2">
+        <v>261</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A262" s="2">
+        <v>262</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A263" s="2">
+        <v>263</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264" s="2">
+        <v>264</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A265" s="2">
+        <v>265</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A266" s="2">
+        <v>266</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267" s="2">
+        <v>267</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268" s="2">
+        <v>268</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269" s="2">
+        <v>269</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270" s="2">
+        <v>270</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271" s="2">
+        <v>271</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A272" s="2">
+        <v>272</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A273" s="2">
+        <v>273</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A274" s="2">
+        <v>274</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A275" s="2">
+        <v>275</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A276" s="2">
+        <v>276</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A277" s="2">
+        <v>277</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A278" s="2">
+        <v>278</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A279" s="2">
+        <v>279</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A280" s="2">
+        <v>280</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A281" s="2">
+        <v>281</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{96CE20C3-9793-4122-9AC2-6F030E0B9A3F}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B60A8C-54BF-4CC8-B2F4-72B7193AB284}">
+  <dimension ref="A1:C312"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="47.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(LibDeb!D:D,Class!A14)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <f>COUNTIF(LibDeb!D:D,Class!A15)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(LibDeb!D:D,Class!A16)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <f>COUNTIF(LibDeb!D:D,Class!A17)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(LibDeb!D:D,Class!A18)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <f>COUNTIF(LibDeb!D:D,Class!A4)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(LibDeb!D:D,Class!A11)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9">
+        <f>COUNTIF(LibDeb!D:D,Class!A12)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10">
+        <f>COUNTIF(LibDeb!D:D,Class!A13)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <f>COUNTIF(LibDeb!D:D,Class!A6)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <f>COUNTIF(LibDeb!D:D,Class!A7)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <f>COUNTIF(LibDeb!D:D,Class!A8)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <f>COUNTIF(LibDeb!D:D,Class!A9)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <f>COUNTIF(LibDeb!D:D,Class!A10)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <f>COUNTIF(LibDeb!D:D,Class!A21)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <f>COUNTIF(LibDeb!D:D,Class!A22)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18">
+        <f>COUNTIF(LibDeb!D:D,Class!A32)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19">
+        <f>COUNTIF(LibDeb!D:D,Class!A19)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20">
+        <f>COUNTIF(LibDeb!D:D,Class!A20)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21">
+        <f>COUNTIF(LibDeb!D:D,Class!A25)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22">
+        <f>COUNTIF(LibDeb!D:D,Class!A26)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23">
+        <f>COUNTIF(LibDeb!D:D,Class!A27)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24">
+        <f>COUNTIF(LibDeb!D:D,Class!A28)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25">
+        <f>COUNTIF(LibDeb!D:D,Class!A29)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26">
+        <f>COUNTIF(LibDeb!D:D,Class!A30)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27">
+        <f>COUNTIF(LibDeb!D:D,Class!A31)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28">
+        <f>COUNTIF(LibDeb!D:D,Class!A24)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29">
+        <f>COUNTIF(LibDeb!D:D,Class!A3)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <f>COUNTIF(LibDeb!D:D,Class!A2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <f>COUNTIF(LibDeb!D:D,Class!A5)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32">
+        <f>COUNTIF(LibDeb!D:D,Class!A23)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33">
+        <f>COUNTIF(LibDeb!D:D,Class!A33)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34">
+        <f>COUNTIF(LibDeb!D:D,Class!A34)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35">
+        <f>COUNTIF(LibDeb!D:D,Class!A35)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36">
+        <f>COUNTIF(LibDeb!D:D,Class!A36)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37">
+        <f>COUNTIF(LibDeb!D:D,Class!A37)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38">
+        <f>COUNTIF(LibDeb!D:D,Class!A38)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39">
+        <f>COUNTIF(LibDeb!D:D,Class!A39)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40">
+        <f>COUNTIF(LibDeb!D:D,Class!A40)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41">
+        <f>COUNTIF(LibDeb!D:D,Class!A41)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42">
+        <f>COUNTIF(LibDeb!D:D,Class!A42)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43">
+        <f>COUNTIF(LibDeb!D:D,Class!A43)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44">
+        <f>COUNTIF(LibDeb!D:D,Class!A44)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45">
+        <f>COUNTIF(LibDeb!D:D,Class!A49)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46">
+        <f>COUNTIF(LibDeb!D:D,Class!A48)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47">
+        <f>COUNTIF(LibDeb!D:D,Class!A47)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48">
+        <f>COUNTIF(LibDeb!D:D,Class!A46)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49">
+        <f>COUNTIF(LibDeb!D:D,Class!A45)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123"/>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139"/>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140"/>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142"/>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143"/>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144"/>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145"/>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146"/>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147"/>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148"/>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149"/>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150"/>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151"/>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152"/>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154"/>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158"/>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159"/>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178"/>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179"/>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180"/>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181"/>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182"/>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183"/>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184"/>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185"/>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192"/>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194"/>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196"/>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197"/>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198"/>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199"/>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200"/>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201"/>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202"/>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203"/>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204"/>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205"/>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206"/>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207"/>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208"/>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209"/>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210"/>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211"/>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212"/>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213"/>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214"/>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215"/>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216"/>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217"/>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218"/>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219"/>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220"/>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221"/>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222"/>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223"/>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224"/>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225"/>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226"/>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A227"/>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A228"/>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A229"/>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A230"/>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A231"/>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A232"/>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A233"/>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A234"/>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A235"/>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A236"/>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A237"/>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A238"/>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A239"/>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A240"/>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A241"/>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242"/>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A243"/>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A244"/>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A245"/>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A246"/>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A247"/>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A248"/>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A249"/>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A250"/>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A251"/>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A252"/>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A253"/>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A254"/>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A255"/>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A256"/>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A257"/>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A258"/>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A259"/>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A260"/>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A261"/>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A262"/>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A263"/>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A264"/>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A265"/>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A266"/>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A267"/>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A268"/>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A269"/>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A270"/>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A271"/>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A272"/>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A273"/>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A274"/>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A275"/>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A276"/>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A277"/>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A278"/>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A279"/>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A280"/>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A281"/>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A282"/>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A283"/>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A284"/>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A285"/>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A286"/>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A287"/>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A288"/>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A289"/>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A290"/>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A291"/>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A292"/>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A293"/>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A294"/>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A295"/>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A296"/>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A297"/>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A298"/>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A299"/>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A300"/>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A301"/>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A302"/>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A303"/>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A304"/>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A305"/>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A306"/>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A307"/>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A308"/>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A309"/>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A310"/>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A311"/>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A312"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{43B60A8C-54BF-4CC8-B2F4-72B7193AB284}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B314">
+    <sortCondition descending="1" ref="B2:B314"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07292F36-2133-48CD-9C2D-2A7F7E937916}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5546875" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C49" xr:uid="{07292F36-2133-48CD-9C2D-2A7F7E937916}">
+    <filterColumn colId="2">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>